--- a/artfynd/A 16314-2025 artfynd.xlsx
+++ b/artfynd/A 16314-2025 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>119402584</v>
       </c>
       <c r="B2" t="n">
-        <v>90846</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -700,12 +695,12 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -781,15 +776,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119402587</v>
+        <v>119402571</v>
       </c>
       <c r="B3" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -797,21 +787,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -821,10 +811,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>563960</v>
+        <v>563918</v>
       </c>
       <c r="R3" t="n">
-        <v>7040312</v>
+        <v>7040450</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -887,15 +877,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119402572</v>
+        <v>119402573</v>
       </c>
       <c r="B4" t="n">
-        <v>78526</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -903,21 +888,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,10 +912,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>563948</v>
+        <v>563867</v>
       </c>
       <c r="R4" t="n">
-        <v>7040451</v>
+        <v>7040399</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -993,15 +978,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119402586</v>
+        <v>119402585</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>83173</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1009,21 +989,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1033,10 +1013,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>563930</v>
+        <v>563823</v>
       </c>
       <c r="R5" t="n">
-        <v>7040329</v>
+        <v>7040352</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1099,37 +1079,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119402573</v>
+        <v>119402572</v>
       </c>
       <c r="B6" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1139,10 +1114,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>563867</v>
+        <v>563948</v>
       </c>
       <c r="R6" t="n">
-        <v>7040399</v>
+        <v>7040451</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1205,37 +1180,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119402585</v>
+        <v>119402587</v>
       </c>
       <c r="B7" t="n">
-        <v>82305</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1245,10 +1215,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>563823</v>
+        <v>563960</v>
       </c>
       <c r="R7" t="n">
-        <v>7040352</v>
+        <v>7040312</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1311,15 +1281,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>119402571</v>
+        <v>119402570</v>
       </c>
       <c r="B8" t="n">
-        <v>90562</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1327,21 +1292,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1351,10 +1316,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>563918</v>
+        <v>563996</v>
       </c>
       <c r="R8" t="n">
-        <v>7040450</v>
+        <v>7040413</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1417,15 +1382,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>119402570</v>
+        <v>119402586</v>
       </c>
       <c r="B9" t="n">
-        <v>79607</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1457,10 +1417,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>563996</v>
+        <v>563930</v>
       </c>
       <c r="R9" t="n">
-        <v>7040413</v>
+        <v>7040329</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>

--- a/artfynd/A 16314-2025 artfynd.xlsx
+++ b/artfynd/A 16314-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -773,6 +778,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402584</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -874,6 +884,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402571</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -975,6 +990,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402573</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1076,6 +1096,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402585</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1177,6 +1202,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402572</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1278,6 +1308,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402587</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1379,6 +1414,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402570</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1480,8 +1520,23 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119402586</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>